--- a/branches/feature/fix-katheter-pce/ValueSet-mii-vs-kardio-extended-condition-severity-snomedct.xlsx
+++ b/branches/feature/fix-katheter-pce/ValueSet-mii-vs-kardio-extended-condition-severity-snomedct.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T14:24:17+00:00</t>
+    <t>2026-10-02T12:47:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature/fix-katheter-pce/ValueSet-mii-vs-kardio-extended-condition-severity-snomedct.xlsx
+++ b/branches/feature/fix-katheter-pce/ValueSet-mii-vs-kardio-extended-condition-severity-snomedct.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T12:47:32+00:00</t>
+    <t>2026-10-02T14:42:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
